--- a/doc/_static/example-files/PMHC-4-0-intake.xlsx
+++ b/doc/_static/example-files/PMHC-4-0-intake.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="103">
   <si>
     <t>key</t>
   </si>
@@ -143,6 +143,9 @@
     <t>BBBBG220219409</t>
   </si>
   <si>
+    <t>C405</t>
+  </si>
+  <si>
     <t>intake_key</t>
   </si>
   <si>
@@ -236,6 +239,9 @@
     <t>12 3</t>
   </si>
   <si>
+    <t>I410</t>
+  </si>
+  <si>
     <t>measure_key</t>
   </si>
   <si>
@@ -312,6 +318,15 @@
   </si>
   <si>
     <t>IarDstIM09</t>
+  </si>
+  <si>
+    <t>2.adult</t>
+  </si>
+  <si>
+    <t>IarDstIM10</t>
+  </si>
+  <si>
+    <t>2.child</t>
   </si>
 </sst>
 </file>
@@ -771,7 +786,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -966,6 +981,38 @@
         <v>6104</v>
       </c>
       <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>99999060620162</v>
+      </c>
+      <c r="D7">
+        <v>6062016</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>9999</v>
+      </c>
+      <c r="I7">
+        <v>6104</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -976,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -984,43 +1031,43 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
         <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1028,7 +1075,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -1058,7 +1105,7 @@
         <v>30072021</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M2" t="s">
         <v>18</v>
@@ -1069,7 +1116,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
@@ -1110,7 +1157,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
@@ -1140,7 +1187,7 @@
         <v>4092021</v>
       </c>
       <c r="L4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M4" t="s">
         <v>18</v>
@@ -1151,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
@@ -1181,7 +1228,7 @@
         <v>5082021</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M5" t="s">
         <v>18</v>
@@ -1192,7 +1239,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
@@ -1222,7 +1269,7 @@
         <v>1092021</v>
       </c>
       <c r="L6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M6" t="s">
         <v>18</v>
@@ -1233,7 +1280,7 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -1263,7 +1310,7 @@
         <v>18082021</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M7" t="s">
         <v>18</v>
@@ -1274,7 +1321,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
@@ -1304,7 +1351,7 @@
         <v>5092021</v>
       </c>
       <c r="L8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
         <v>18</v>
@@ -1315,7 +1362,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -1345,7 +1392,7 @@
         <v>21022021</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M9" t="s">
         <v>18</v>
@@ -1356,7 +1403,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
@@ -1386,7 +1433,7 @@
         <v>12102021</v>
       </c>
       <c r="L10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M10" t="s">
         <v>18</v>
@@ -1397,7 +1444,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -1427,10 +1474,42 @@
         <v>12052021</v>
       </c>
       <c r="L11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M11" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>12062024</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>12062024</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1440,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1448,46 +1527,46 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1495,10 +1574,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1528,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N2">
         <v>3</v>
@@ -1539,10 +1618,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1572,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N3">
         <v>9</v>
@@ -1583,10 +1662,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1627,10 +1706,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1660,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -1671,10 +1750,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1715,10 +1794,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1748,7 +1827,7 @@
         <v>2</v>
       </c>
       <c r="M7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N7">
         <v>3</v>
@@ -1759,10 +1838,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1803,10 +1882,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1847,10 +1926,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1880,7 +1959,7 @@
         <v>4</v>
       </c>
       <c r="M10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N10">
         <v>4</v>
@@ -1891,13 +1970,13 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1924,9 +2003,53 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12">
         <v>3</v>
       </c>
     </row>
